--- a/Carbon/Mass.xlsx
+++ b/Carbon/Mass.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lukaseamus/Desktop/PhD/Papers/Burial/kelp-burial/Carbon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61057766-990D-D44C-AC28-7DDA70E34B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92AC749B-BC3C-C040-B523-B01811923D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6300" yWindow="2060" windowWidth="28040" windowHeight="17440" xr2:uid="{D120C0EF-290F-244A-AE4B-CB2F7CD281C3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="1055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="1054">
   <si>
     <t>ID</t>
   </si>
@@ -990,9 +990,6 @@
   </si>
   <si>
     <t>Mass</t>
-  </si>
-  <si>
-    <t>119..22088</t>
   </si>
   <si>
     <t>E_C_1_1_1</t>
@@ -7113,7 +7110,7 @@
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B437">
         <v>111.26385999999999</v>
@@ -7121,7 +7118,7 @@
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B438">
         <v>145.45654999999999</v>
@@ -7129,7 +7126,7 @@
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B439">
         <v>89.143979999999999</v>
@@ -7137,7 +7134,7 @@
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B440">
         <v>103.63549999999999</v>
@@ -7145,7 +7142,7 @@
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B441">
         <v>126.99405</v>
@@ -7153,7 +7150,7 @@
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B442">
         <v>124.50265</v>
@@ -7161,7 +7158,7 @@
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B443">
         <v>171.3956</v>
@@ -7169,7 +7166,7 @@
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B444">
         <v>140.70054999999999</v>
@@ -7177,7 +7174,7 @@
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B445">
         <v>134.45304999999999</v>
@@ -7185,7 +7182,7 @@
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B446">
         <v>122.33540000000001</v>
@@ -7193,7 +7190,7 @@
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B447">
         <v>146.32855000000001</v>
@@ -7201,7 +7198,7 @@
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B448">
         <v>138.66495</v>
@@ -7209,7 +7206,7 @@
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B449">
         <v>163.1677</v>
@@ -7217,7 +7214,7 @@
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B450">
         <v>133.25995</v>
@@ -7225,7 +7222,7 @@
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B451">
         <v>137.22595000000001</v>
@@ -7233,7 +7230,7 @@
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B452">
         <v>130.71645000000001</v>
@@ -7241,7 +7238,7 @@
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B453">
         <v>113.55231999999999</v>
@@ -7249,7 +7246,7 @@
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B454">
         <v>123.6271</v>
@@ -7257,7 +7254,7 @@
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B455">
         <v>110.39574</v>
@@ -7265,7 +7262,7 @@
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B456">
         <v>188.12705</v>
@@ -7273,7 +7270,7 @@
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B457">
         <v>86.606080000000006</v>
@@ -7281,7 +7278,7 @@
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B458">
         <v>91.188019999999995</v>
@@ -7289,7 +7286,7 @@
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B459">
         <v>75.277659999999997</v>
@@ -7297,7 +7294,7 @@
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B460">
         <v>92.936019999999999</v>
@@ -7305,7 +7302,7 @@
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B461">
         <v>75.268780000000007</v>
@@ -7313,7 +7310,7 @@
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B462">
         <v>93.02664</v>
@@ -7321,7 +7318,7 @@
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B463">
         <v>89.878380000000007</v>
@@ -7329,7 +7326,7 @@
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B464">
         <v>89.707040000000006</v>
@@ -7337,7 +7334,7 @@
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B465">
         <v>80.359319999999997</v>
@@ -7345,7 +7342,7 @@
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B466">
         <v>85.390339999999995</v>
@@ -7353,7 +7350,7 @@
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B467">
         <v>96.076520000000002</v>
@@ -7361,7 +7358,7 @@
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B468">
         <v>97.300020000000004</v>
@@ -7369,7 +7366,7 @@
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B469">
         <v>122.65495</v>
@@ -7377,7 +7374,7 @@
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B470">
         <v>102.2277</v>
@@ -7385,7 +7382,7 @@
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B471">
         <v>72.67774</v>
@@ -7393,7 +7390,7 @@
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B472">
         <v>130.35055</v>
@@ -7401,7 +7398,7 @@
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B473">
         <v>108.79888</v>
@@ -7409,7 +7406,7 @@
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B474">
         <v>103.59156</v>
@@ -7417,7 +7414,7 @@
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B475">
         <v>137.44575</v>
@@ -7425,7 +7422,7 @@
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B476">
         <v>105.72178</v>
@@ -7433,7 +7430,7 @@
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B477">
         <v>101.11192</v>
@@ -7441,7 +7438,7 @@
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B478">
         <v>397.58300000000003</v>
@@ -7449,7 +7446,7 @@
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B479">
         <v>69.355400000000003</v>
@@ -7457,7 +7454,7 @@
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B480">
         <v>77.952619999999996</v>
@@ -7465,7 +7462,7 @@
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B481">
         <v>89.379059999999996</v>
@@ -7473,7 +7470,7 @@
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B482">
         <v>98.371939999999995</v>
@@ -7481,7 +7478,7 @@
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B483">
         <v>93.455079999999995</v>
@@ -7489,7 +7486,7 @@
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B484">
         <v>88.939959999999999</v>
@@ -7497,7 +7494,7 @@
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B485">
         <v>84.098439999999997</v>
@@ -7505,7 +7502,7 @@
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B486">
         <v>75.609459999999999</v>
@@ -7513,7 +7510,7 @@
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B487">
         <v>95.164180000000002</v>
@@ -7521,7 +7518,7 @@
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B488">
         <v>81.757239999999996</v>
@@ -7529,7 +7526,7 @@
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B489">
         <v>101.93268</v>
@@ -7537,7 +7534,7 @@
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B490">
         <v>88.538439999999994</v>
@@ -7545,7 +7542,7 @@
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B491">
         <v>103.56872</v>
@@ -7553,7 +7550,7 @@
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B492">
         <v>118.60212</v>
@@ -7561,7 +7558,7 @@
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B493">
         <v>94.432339999999996</v>
@@ -7569,7 +7566,7 @@
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B494">
         <v>106.34116</v>
@@ -7577,7 +7574,7 @@
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B495">
         <v>115.40886</v>
@@ -7585,7 +7582,7 @@
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B496">
         <v>99.447419999999994</v>
@@ -7593,7 +7590,7 @@
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B497">
         <v>105.75734</v>
@@ -7601,7 +7598,7 @@
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B498">
         <v>107.37276</v>
@@ -7609,7 +7606,7 @@
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B499">
         <v>292.38200000000001</v>
@@ -7617,7 +7614,7 @@
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B500">
         <v>41.01502</v>
@@ -7625,7 +7622,7 @@
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B501">
         <v>76.961200000000005</v>
@@ -7633,7 +7630,7 @@
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B502">
         <v>95.187219999999996</v>
@@ -7641,7 +7638,7 @@
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B503">
         <v>82.710880000000003</v>
@@ -7649,7 +7646,7 @@
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B504">
         <v>90.521720000000002</v>
@@ -7657,7 +7654,7 @@
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B505">
         <v>84.509039999999999</v>
@@ -7665,7 +7662,7 @@
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B506">
         <v>85.206879999999998</v>
@@ -7673,7 +7670,7 @@
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B507">
         <v>95.215540000000004</v>
@@ -7681,7 +7678,7 @@
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B508">
         <v>94.245440000000002</v>
@@ -7689,7 +7686,7 @@
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B509">
         <v>94.736760000000004</v>
@@ -7697,7 +7694,7 @@
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B510">
         <v>101.05888</v>
@@ -7705,7 +7702,7 @@
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B511">
         <v>117.03466</v>
@@ -7713,7 +7710,7 @@
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B512">
         <v>110.09774</v>
@@ -7721,7 +7718,7 @@
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B513">
         <v>102.45847999999999</v>
@@ -7729,7 +7726,7 @@
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B514">
         <v>106.97668</v>
@@ -7737,7 +7734,7 @@
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B515">
         <v>126.74275</v>
@@ -7745,7 +7742,7 @@
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B516">
         <v>92.620080000000002</v>
@@ -7753,7 +7750,7 @@
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B517">
         <v>100.81476000000001</v>
@@ -7761,7 +7758,7 @@
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B518">
         <v>96.130840000000006</v>
@@ -7769,7 +7766,7 @@
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B519">
         <v>99.213560000000001</v>
@@ -7777,7 +7774,7 @@
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B520">
         <v>467.83100000000002</v>
@@ -7785,7 +7782,7 @@
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B521">
         <v>42.257010000000001</v>
@@ -7793,7 +7790,7 @@
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B522">
         <v>65.690960000000004</v>
@@ -7801,7 +7798,7 @@
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B523">
         <v>83.74588</v>
@@ -7809,7 +7806,7 @@
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B524">
         <v>78.295879999999997</v>
@@ -7817,7 +7814,7 @@
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B525">
         <v>91.551860000000005</v>
@@ -7825,7 +7822,7 @@
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B526">
         <v>78.657079999999993</v>
@@ -7833,7 +7830,7 @@
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B527">
         <v>95.248059999999995</v>
@@ -7841,7 +7838,7 @@
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B528">
         <v>56.058900000000001</v>
@@ -7849,7 +7846,7 @@
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B529">
         <v>95.086839999999995</v>
@@ -7857,7 +7854,7 @@
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B530">
         <v>96.152199999999993</v>
@@ -7865,7 +7862,7 @@
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B531">
         <v>87.737899999999996</v>
@@ -7873,7 +7870,7 @@
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B532">
         <v>112.64704</v>
@@ -7881,7 +7878,7 @@
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B533">
         <v>81.382859999999994</v>
@@ -7889,7 +7886,7 @@
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B534">
         <v>118.81413999999999</v>
@@ -7897,7 +7894,7 @@
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B535">
         <v>106.95926</v>
@@ -7905,7 +7902,7 @@
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B536">
         <v>112.78022</v>
@@ -7913,7 +7910,7 @@
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B537">
         <v>95.837999999999994</v>
@@ -7921,7 +7918,7 @@
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B538">
         <v>92.742639999999994</v>
@@ -7929,7 +7926,7 @@
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B539">
         <v>122.77785</v>
@@ -7937,7 +7934,7 @@
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B540">
         <v>103.39774</v>
@@ -7945,7 +7942,7 @@
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B541">
         <v>459.73399999999998</v>
@@ -7953,7 +7950,7 @@
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B542">
         <v>72.683580000000006</v>
@@ -7961,7 +7958,7 @@
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B543">
         <v>93.525959999999998</v>
@@ -7969,7 +7966,7 @@
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B544">
         <v>84.085359999999994</v>
@@ -7977,7 +7974,7 @@
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B545">
         <v>109.62474</v>
@@ -7985,7 +7982,7 @@
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B546">
         <v>88.602919999999997</v>
@@ -7993,7 +7990,7 @@
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B547">
         <v>90.226119999999995</v>
@@ -8001,7 +7998,7 @@
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B548">
         <v>78.019279999999995</v>
@@ -8009,7 +8006,7 @@
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B549">
         <v>79.155739999999994</v>
@@ -8017,7 +8014,7 @@
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B550">
         <v>96.785780000000003</v>
@@ -8025,7 +8022,7 @@
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B551">
         <v>93.796499999999995</v>
@@ -8033,7 +8030,7 @@
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B552">
         <v>99.948319999999995</v>
@@ -8041,7 +8038,7 @@
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B553">
         <v>105.9006</v>
@@ -8049,7 +8046,7 @@
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B554">
         <v>98.0886</v>
@@ -8057,7 +8054,7 @@
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B555">
         <v>108.11262000000001</v>
@@ -8065,7 +8062,7 @@
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B556">
         <v>90.599599999999995</v>
@@ -8073,7 +8070,7 @@
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B557">
         <v>127.8306</v>
@@ -8081,7 +8078,7 @@
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B558">
         <v>101.99592</v>
@@ -8089,7 +8086,7 @@
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B559">
         <v>103.45374</v>
@@ -8097,7 +8094,7 @@
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B560">
         <v>95.600880000000004</v>
@@ -8105,7 +8102,7 @@
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B561">
         <v>77.157700000000006</v>
@@ -8113,7 +8110,7 @@
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B562">
         <v>738.8</v>
@@ -8121,7 +8118,7 @@
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B563">
         <v>126.95175</v>
@@ -8129,7 +8126,7 @@
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B564">
         <v>161.43889999999999</v>
@@ -8137,7 +8134,7 @@
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B565">
         <v>122.9893</v>
@@ -8145,7 +8142,7 @@
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B566">
         <v>113.23962</v>
@@ -8153,7 +8150,7 @@
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B567">
         <v>127.52185</v>
@@ -8161,7 +8158,7 @@
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B568">
         <v>134.36510000000001</v>
@@ -8169,7 +8166,7 @@
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B569">
         <v>117.9862</v>
@@ -8177,7 +8174,7 @@
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B570">
         <v>155.28569999999999</v>
@@ -8185,7 +8182,7 @@
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B571">
         <v>118.22242</v>
@@ -8193,7 +8190,7 @@
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B572">
         <v>92.624139999999997</v>
@@ -8201,7 +8198,7 @@
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B573">
         <v>155.47219999999999</v>
@@ -8209,7 +8206,7 @@
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B574">
         <v>123.2961</v>
@@ -8217,7 +8214,7 @@
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B575">
         <v>125.21165000000001</v>
@@ -8225,7 +8222,7 @@
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B576">
         <v>99.158360000000002</v>
@@ -8233,7 +8230,7 @@
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B577">
         <v>108.90566</v>
@@ -8241,7 +8238,7 @@
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B578">
         <v>134.41655</v>
@@ -8249,7 +8246,7 @@
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B579">
         <v>150.83805000000001</v>
@@ -8257,7 +8254,7 @@
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B580">
         <v>133.59975</v>
@@ -8265,7 +8262,7 @@
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B581">
         <v>140.49164999999999</v>
@@ -8273,7 +8270,7 @@
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B582">
         <v>161.7671</v>
@@ -8281,7 +8278,7 @@
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B583">
         <v>588.1</v>
@@ -8289,7 +8286,7 @@
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B584">
         <v>109.28642000000001</v>
@@ -8297,7 +8294,7 @@
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B585">
         <v>79.151560000000003</v>
@@ -8305,7 +8302,7 @@
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B586">
         <v>95.413300000000007</v>
@@ -8313,7 +8310,7 @@
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B587">
         <v>93.613919999999993</v>
@@ -8321,7 +8318,7 @@
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B588">
         <v>91.149439999999998</v>
@@ -8329,7 +8326,7 @@
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B589">
         <v>87.740740000000002</v>
@@ -8337,7 +8334,7 @@
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B590">
         <v>94.196860000000001</v>
@@ -8345,7 +8342,7 @@
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B591">
         <v>79.544079999999994</v>
@@ -8353,7 +8350,7 @@
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B592">
         <v>93.178780000000003</v>
@@ -8361,7 +8358,7 @@
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B593">
         <v>106.01846</v>
@@ -8369,7 +8366,7 @@
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B594">
         <v>96.072860000000006</v>
@@ -8377,7 +8374,7 @@
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B595">
         <v>98.157300000000006</v>
@@ -8385,7 +8382,7 @@
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B596">
         <v>102.78712</v>
@@ -8393,7 +8390,7 @@
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B597">
         <v>110.96746</v>
@@ -8401,7 +8398,7 @@
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B598">
         <v>106.53848000000001</v>
@@ -8409,7 +8406,7 @@
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B599">
         <v>117.22662</v>
@@ -8417,7 +8414,7 @@
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B600">
         <v>137.10075000000001</v>
@@ -8425,7 +8422,7 @@
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B601">
         <v>102.65814</v>
@@ -8433,7 +8430,7 @@
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B602">
         <v>103.5449</v>
@@ -8441,7 +8438,7 @@
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B603">
         <v>106.81356</v>
@@ -8449,7 +8446,7 @@
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B604">
         <v>181.09115</v>
@@ -8457,7 +8454,7 @@
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B605">
         <v>91.916060000000002</v>
@@ -8465,7 +8462,7 @@
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B606">
         <v>118.04746</v>
@@ -8473,7 +8470,7 @@
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B607">
         <v>114.48650000000001</v>
@@ -8481,7 +8478,7 @@
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B608">
         <v>126.54805</v>
@@ -8489,7 +8486,7 @@
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A609" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B609">
         <v>118.92862</v>
@@ -8497,7 +8494,7 @@
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A610" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B610">
         <v>129.67259999999999</v>
@@ -8505,7 +8502,7 @@
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B611">
         <v>126.30844999999999</v>
@@ -8513,7 +8510,7 @@
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B612">
         <v>152.37815000000001</v>
@@ -8521,7 +8518,7 @@
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B613">
         <v>126.4216</v>
@@ -8529,7 +8526,7 @@
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B614">
         <v>119.08110000000001</v>
@@ -8537,7 +8534,7 @@
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B615">
         <v>123.33795000000001</v>
@@ -8545,7 +8542,7 @@
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B616">
         <v>165.09125</v>
@@ -8553,7 +8550,7 @@
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B617">
         <v>128.48705000000001</v>
@@ -8561,7 +8558,7 @@
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B618">
         <v>145.7722</v>
@@ -8569,7 +8566,7 @@
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B619">
         <v>117.70068000000001</v>
@@ -8577,7 +8574,7 @@
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B620">
         <v>115.92113999999999</v>
@@ -8585,7 +8582,7 @@
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A621" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B621">
         <v>148.09795</v>
@@ -8593,7 +8590,7 @@
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A622" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B622">
         <v>165.34545</v>
@@ -8601,7 +8598,7 @@
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B623">
         <v>119.67012</v>
@@ -8609,7 +8606,7 @@
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B624">
         <v>146.29235</v>
@@ -8617,7 +8614,7 @@
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B625">
         <v>295.45400000000001</v>
@@ -8625,7 +8622,7 @@
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B626">
         <v>78.565380000000005</v>
@@ -8633,7 +8630,7 @@
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B627">
         <v>74.036180000000002</v>
@@ -8641,7 +8638,7 @@
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B628">
         <v>86.014840000000007</v>
@@ -8649,7 +8646,7 @@
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B629">
         <v>75.562259999999995</v>
@@ -8657,7 +8654,7 @@
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B630">
         <v>85.853880000000004</v>
@@ -8665,7 +8662,7 @@
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A631" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B631">
         <v>87.450800000000001</v>
@@ -8673,7 +8670,7 @@
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B632">
         <v>85.339979999999997</v>
@@ -8681,7 +8678,7 @@
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A633" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B633">
         <v>79.353939999999994</v>
@@ -8689,7 +8686,7 @@
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A634" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B634">
         <v>90.59478</v>
@@ -8697,7 +8694,7 @@
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B635">
         <v>101.74278</v>
@@ -8705,7 +8702,7 @@
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B636">
         <v>89.847319999999996</v>
@@ -8713,7 +8710,7 @@
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A637" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B637">
         <v>127.26765</v>
@@ -8721,7 +8718,7 @@
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A638" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B638">
         <v>137.47720000000001</v>
@@ -8729,7 +8726,7 @@
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A639" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B639">
         <v>87.609340000000003</v>
@@ -8737,7 +8734,7 @@
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A640" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B640">
         <v>100.76828</v>
@@ -8745,7 +8742,7 @@
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A641" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B641">
         <v>120.38535</v>
@@ -8753,7 +8750,7 @@
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A642" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B642">
         <v>106.92668</v>
@@ -8761,7 +8758,7 @@
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A643" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B643">
         <v>102.1555</v>
@@ -8769,7 +8766,7 @@
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A644" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B644" s="4">
         <v>112.91502</v>
@@ -8777,7 +8774,7 @@
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A645" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B645">
         <v>132.14070000000001</v>
@@ -8785,7 +8782,7 @@
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B646">
         <v>352.10399999999998</v>
@@ -8793,7 +8790,7 @@
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B647">
         <v>146.9179</v>
@@ -8801,7 +8798,7 @@
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B648">
         <v>122.94875</v>
@@ -8809,7 +8806,7 @@
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A649" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B649">
         <v>113.91394</v>
@@ -8817,7 +8814,7 @@
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B650">
         <v>117.24804</v>
@@ -8825,7 +8822,7 @@
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B651">
         <v>122.37295</v>
@@ -8833,7 +8830,7 @@
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A652" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B652">
         <v>124.3583</v>
@@ -8841,7 +8838,7 @@
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A653" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B653">
         <v>103.03534000000001</v>
@@ -8849,7 +8846,7 @@
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A654" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B654">
         <v>105.76308</v>
@@ -8857,7 +8854,7 @@
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A655" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B655">
         <v>134.32515000000001</v>
@@ -8865,7 +8862,7 @@
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A656" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B656">
         <v>124.90465</v>
@@ -8873,7 +8870,7 @@
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A657" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B657">
         <v>129.30035000000001</v>
@@ -8881,7 +8878,7 @@
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A658" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B658">
         <v>113.10498</v>
@@ -8889,7 +8886,7 @@
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A659" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B659">
         <v>119.03428</v>
@@ -8897,7 +8894,7 @@
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A660" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B660">
         <v>132.2347</v>
@@ -8905,7 +8902,7 @@
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A661" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B661">
         <v>107.25485999999999</v>
@@ -8913,7 +8910,7 @@
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A662" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B662">
         <v>123.6228</v>
@@ -8921,7 +8918,7 @@
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A663" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B663">
         <v>125.1628</v>
@@ -8929,7 +8926,7 @@
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A664" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B664">
         <v>129.05955</v>
@@ -8937,7 +8934,7 @@
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A665" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B665">
         <v>116.93002</v>
@@ -8945,7 +8942,7 @@
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A666" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B666">
         <v>117.06442</v>
@@ -8953,7 +8950,7 @@
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A667" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B667">
         <v>655.29999999999995</v>
@@ -8961,7 +8958,7 @@
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A668" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B668">
         <v>98.858059999999995</v>
@@ -8969,7 +8966,7 @@
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A669" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B669">
         <v>78.151120000000006</v>
@@ -8977,7 +8974,7 @@
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A670" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B670">
         <v>96.048519999999996</v>
@@ -8985,7 +8982,7 @@
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A671" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B671">
         <v>75.316659999999999</v>
@@ -8993,7 +8990,7 @@
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A672" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B672">
         <v>85.470259999999996</v>
@@ -9001,7 +8998,7 @@
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A673" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B673">
         <v>88.168760000000006</v>
@@ -9009,7 +9006,7 @@
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A674" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B674">
         <v>96.273020000000002</v>
@@ -9017,7 +9014,7 @@
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A675" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B675">
         <v>104.15988</v>
@@ -9025,7 +9022,7 @@
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A676" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B676">
         <v>101.8028</v>
@@ -9033,7 +9030,7 @@
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A677" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B677">
         <v>91.337980000000002</v>
@@ -9041,7 +9038,7 @@
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A678" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B678">
         <v>97.250200000000007</v>
@@ -9049,7 +9046,7 @@
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A679" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B679">
         <v>106.69762</v>
@@ -9057,7 +9054,7 @@
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A680" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B680">
         <v>116.20362</v>
@@ -9065,7 +9062,7 @@
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A681" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B681">
         <v>118.23314000000001</v>
@@ -9073,7 +9070,7 @@
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A682" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B682">
         <v>98.784379999999999</v>
@@ -9081,7 +9078,7 @@
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A683" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B683">
         <v>101.23578000000001</v>
@@ -9089,7 +9086,7 @@
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A684" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B684">
         <v>109.60317999999999</v>
@@ -9097,7 +9094,7 @@
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A685" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B685">
         <v>111.01613999999999</v>
@@ -9105,7 +9102,7 @@
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A686" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B686">
         <v>121.71510000000001</v>
@@ -9113,7 +9110,7 @@
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A687" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B687">
         <v>118.72198</v>
@@ -9121,7 +9118,7 @@
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A688" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B688">
         <v>469.77699999999999</v>
@@ -9129,7 +9126,7 @@
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A689" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B689">
         <v>98.653700000000001</v>
@@ -9137,7 +9134,7 @@
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A690" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B690">
         <v>119.19144</v>
@@ -9145,7 +9142,7 @@
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A691" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B691">
         <v>101.37835</v>
@@ -9153,7 +9150,7 @@
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A692" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B692">
         <v>151.44835</v>
@@ -9161,7 +9158,7 @@
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A693" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B693">
         <v>112.97308</v>
@@ -9169,7 +9166,7 @@
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A694" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B694">
         <v>124.73815</v>
@@ -9177,7 +9174,7 @@
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A695" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B695">
         <v>141.39330000000001</v>
@@ -9185,7 +9182,7 @@
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A696" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B696">
         <v>123.10894999999999</v>
@@ -9193,7 +9190,7 @@
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A697" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B697">
         <v>123.40235</v>
@@ -9201,7 +9198,7 @@
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A698" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B698">
         <v>122.39055</v>
@@ -9209,7 +9206,7 @@
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A699" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B699">
         <v>130.6062</v>
@@ -9217,7 +9214,7 @@
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A700" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B700">
         <v>124.74455</v>
@@ -9225,7 +9222,7 @@
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A701" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B701">
         <v>123.6944</v>
@@ -9233,7 +9230,7 @@
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A702" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B702">
         <v>154.79169999999999</v>
@@ -9241,7 +9238,7 @@
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A703" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B703">
         <v>144.1377</v>
@@ -9249,7 +9246,7 @@
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A704" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B704">
         <v>144.11369999999999</v>
@@ -9257,7 +9254,7 @@
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A705" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B705">
         <v>138.54395</v>
@@ -9265,7 +9262,7 @@
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A706" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B706">
         <v>149.68459999999999</v>
@@ -9273,7 +9270,7 @@
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A707" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B707">
         <v>132.79124999999999</v>
@@ -9281,7 +9278,7 @@
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A708" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B708">
         <v>129.87129999999999</v>
@@ -9289,7 +9286,7 @@
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A709" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B709">
         <v>791.4</v>
@@ -9297,7 +9294,7 @@
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A710" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B710">
         <v>106.69762</v>
@@ -9305,7 +9302,7 @@
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A711" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B711">
         <v>120.69605</v>
@@ -9313,7 +9310,7 @@
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A712" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B712">
         <v>84.693439999999995</v>
@@ -9321,7 +9318,7 @@
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A713" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B713">
         <v>75.933419999999998</v>
@@ -9329,7 +9326,7 @@
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A714" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B714">
         <v>72.809780000000003</v>
@@ -9337,7 +9334,7 @@
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A715" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B715">
         <v>79.433400000000006</v>
@@ -9345,7 +9342,7 @@
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A716" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B716">
         <v>70.793180000000007</v>
@@ -9353,7 +9350,7 @@
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A717" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B717">
         <v>94.466499999999996</v>
@@ -9361,7 +9358,7 @@
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A718" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B718">
         <v>86.370699999999999</v>
@@ -9369,7 +9366,7 @@
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A719" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B719">
         <v>104.29747999999999</v>
@@ -9377,7 +9374,7 @@
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A720" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B720">
         <v>98.662639999999996</v>
@@ -9385,7 +9382,7 @@
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A721" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B721">
         <v>96.648899999999998</v>
@@ -9393,7 +9390,7 @@
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A722" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B722">
         <v>97.732079999999996</v>
@@ -9401,7 +9398,7 @@
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A723" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B723">
         <v>108.04564000000001</v>
@@ -9409,7 +9406,7 @@
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A724" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B724">
         <v>109.49826</v>
@@ -9417,7 +9414,7 @@
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A725" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B725">
         <v>95.906480000000002</v>
@@ -9425,7 +9422,7 @@
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A726" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B726">
         <v>110.36874</v>
@@ -9433,7 +9430,7 @@
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A727" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B727">
         <v>116.69278</v>
@@ -9441,7 +9438,7 @@
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A728" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B728">
         <v>98.507300000000001</v>
@@ -9449,7 +9446,7 @@
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A729" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B729">
         <v>108.61948</v>
@@ -9457,7 +9454,7 @@
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A730" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B730">
         <v>406.59800000000001</v>
@@ -9465,7 +9462,7 @@
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A731" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B731">
         <v>314.404</v>
@@ -9473,7 +9470,7 @@
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A732" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B732">
         <v>131.92175</v>
@@ -9481,7 +9478,7 @@
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A733" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B733">
         <v>136.56720000000001</v>
@@ -9489,7 +9486,7 @@
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A734" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B734">
         <v>139.85284999999999</v>
@@ -9497,7 +9494,7 @@
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A735" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B735">
         <v>133.54564999999999</v>
@@ -9505,7 +9502,7 @@
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A736" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B736">
         <v>117.42522</v>
@@ -9513,7 +9510,7 @@
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A737" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B737">
         <v>136.67869999999999</v>
@@ -9521,7 +9518,7 @@
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A738" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B738">
         <v>140.8587</v>
@@ -9529,7 +9526,7 @@
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A739" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B739">
         <v>133.0736</v>
@@ -9537,7 +9534,7 @@
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A740" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B740">
         <v>123.7295</v>
@@ -9545,7 +9542,7 @@
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A741" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B741">
         <v>136.18029999999999</v>
@@ -9553,7 +9550,7 @@
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A742" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B742">
         <v>111.08056000000001</v>
@@ -9561,7 +9558,7 @@
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A743" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B743">
         <v>130.84200000000001</v>
@@ -9569,7 +9566,7 @@
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A744" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B744">
         <v>136.41555</v>
@@ -9577,7 +9574,7 @@
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A745" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B745">
         <v>146.31211999999999</v>
@@ -9585,7 +9582,7 @@
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A746" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B746">
         <v>114.98062</v>
@@ -9593,7 +9590,7 @@
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A747" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B747">
         <v>130.70703</v>
@@ -9601,7 +9598,7 @@
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A748" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B748">
         <v>124.0231</v>
@@ -9609,7 +9606,7 @@
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A749" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B749">
         <v>133.38355000000001</v>
@@ -9617,7 +9614,7 @@
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A750" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B750">
         <v>142.86944</v>
@@ -9625,7 +9622,7 @@
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A751" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B751">
         <v>490.3</v>
@@ -9633,7 +9630,7 @@
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A752" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B752">
         <v>105.08578</v>
@@ -9641,7 +9638,7 @@
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A753" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B753">
         <v>80.992840000000001</v>
@@ -9649,7 +9646,7 @@
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A754" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B754">
         <v>89.439920000000001</v>
@@ -9657,7 +9654,7 @@
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A755" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B755">
         <v>78.215019999999996</v>
@@ -9665,7 +9662,7 @@
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A756" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B756">
         <v>82.667839999999998</v>
@@ -9673,7 +9670,7 @@
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A757" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B757">
         <v>110.97544000000001</v>
@@ -9681,7 +9678,7 @@
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A758" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B758">
         <v>87.120400000000004</v>
@@ -9689,7 +9686,7 @@
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A759" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B759">
         <v>92.269760000000005</v>
@@ -9697,7 +9694,7 @@
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A760" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B760">
         <v>85.165319999999994</v>
@@ -9705,7 +9702,7 @@
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A761" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B761">
         <v>90.881919999999994</v>
@@ -9713,7 +9710,7 @@
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A762" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B762">
         <v>89.904780000000002</v>
@@ -9721,7 +9718,7 @@
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A763" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B763">
         <v>84.50506</v>
@@ -9729,7 +9726,7 @@
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A764" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B764">
         <v>79.416319999999999</v>
@@ -9737,7 +9734,7 @@
     </row>
     <row r="765" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A765" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B765">
         <v>104.8917</v>
@@ -9745,7 +9742,7 @@
     </row>
     <row r="766" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A766" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B766">
         <v>105.01662</v>
@@ -9753,7 +9750,7 @@
     </row>
     <row r="767" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A767" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B767">
         <v>104.73866</v>
@@ -9761,7 +9758,7 @@
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A768" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B768">
         <v>104.03646000000001</v>
@@ -9769,7 +9766,7 @@
     </row>
     <row r="769" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A769" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B769">
         <v>126.40734999999999</v>
@@ -9777,7 +9774,7 @@
     </row>
     <row r="770" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A770" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B770">
         <v>117.7189</v>
@@ -9785,7 +9782,7 @@
     </row>
     <row r="771" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A771" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B771">
         <v>114.72154</v>
@@ -9793,7 +9790,7 @@
     </row>
     <row r="772" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A772" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B772">
         <v>323.21300000000002</v>
@@ -9801,7 +9798,7 @@
     </row>
     <row r="773" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A773" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B773">
         <v>165.15514999999999</v>
@@ -9809,7 +9806,7 @@
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A774" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B774">
         <v>129.57315</v>
@@ -9817,7 +9814,7 @@
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A775" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B775">
         <v>165.87479999999999</v>
@@ -9825,7 +9822,7 @@
     </row>
     <row r="776" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A776" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B776">
         <v>135.60995</v>
@@ -9833,7 +9830,7 @@
     </row>
     <row r="777" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A777" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B777">
         <v>133.00915000000001</v>
@@ -9841,7 +9838,7 @@
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A778" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B778">
         <v>128.91524999999999</v>
@@ -9849,7 +9846,7 @@
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A779" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B779">
         <v>143.36824999999999</v>
@@ -9857,7 +9854,7 @@
     </row>
     <row r="780" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A780" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B780">
         <v>142.96459999999999</v>
@@ -9865,7 +9862,7 @@
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A781" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B781">
         <v>133.61750000000001</v>
@@ -9873,7 +9870,7 @@
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A782" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B782">
         <v>134.46985000000001</v>
@@ -9881,7 +9878,7 @@
     </row>
     <row r="783" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A783" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B783">
         <v>113.84045999999999</v>
@@ -9889,7 +9886,7 @@
     </row>
     <row r="784" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A784" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B784">
         <v>130.00274999999999</v>
@@ -9897,7 +9894,7 @@
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A785" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B785">
         <v>135.26935</v>
@@ -9905,7 +9902,7 @@
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A786" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B786">
         <v>136.38645</v>
@@ -9913,7 +9910,7 @@
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A787" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B787">
         <v>118.27776</v>
@@ -9921,7 +9918,7 @@
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A788" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B788">
         <v>126.54485</v>
@@ -9929,7 +9926,7 @@
     </row>
     <row r="789" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A789" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B789">
         <v>120.00995</v>
@@ -9937,7 +9934,7 @@
     </row>
     <row r="790" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A790" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B790">
         <v>109.16336</v>
@@ -9945,7 +9942,7 @@
     </row>
     <row r="791" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A791" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B791">
         <v>105.41088000000001</v>
@@ -9953,7 +9950,7 @@
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A792" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B792">
         <v>130.94765000000001</v>
@@ -9961,7 +9958,7 @@
     </row>
     <row r="793" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A793" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B793">
         <v>588.9</v>
@@ -9969,7 +9966,7 @@
     </row>
     <row r="794" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A794" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B794">
         <v>106.91379999999999</v>
@@ -9977,7 +9974,7 @@
     </row>
     <row r="795" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A795" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B795">
         <v>80.156480000000002</v>
@@ -9985,7 +9982,7 @@
     </row>
     <row r="796" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A796" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B796">
         <v>112.7903</v>
@@ -9993,7 +9990,7 @@
     </row>
     <row r="797" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A797" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B797">
         <v>60.177599999999998</v>
@@ -10001,7 +9998,7 @@
     </row>
     <row r="798" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A798" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B798">
         <v>86.133880000000005</v>
@@ -10009,7 +10006,7 @@
     </row>
     <row r="799" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A799" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B799">
         <v>78.62876</v>
@@ -10017,7 +10014,7 @@
     </row>
     <row r="800" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A800" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B800">
         <v>114.44722</v>
@@ -10025,7 +10022,7 @@
     </row>
     <row r="801" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A801" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B801">
         <v>87.752740000000003</v>
@@ -10033,7 +10030,7 @@
     </row>
     <row r="802" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A802" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B802">
         <v>121.53685</v>
@@ -10041,7 +10038,7 @@
     </row>
     <row r="803" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A803" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B803">
         <v>85.110479999999995</v>
@@ -10049,7 +10046,7 @@
     </row>
     <row r="804" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A804" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B804">
         <v>118.79862</v>
@@ -10057,7 +10054,7 @@
     </row>
     <row r="805" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A805" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B805">
         <v>115.90971999999999</v>
@@ -10065,7 +10062,7 @@
     </row>
     <row r="806" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A806" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B806">
         <v>107.49169999999999</v>
@@ -10073,7 +10070,7 @@
     </row>
     <row r="807" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A807" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B807">
         <v>122.68495</v>
@@ -10081,7 +10078,7 @@
     </row>
     <row r="808" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A808" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B808">
         <v>104.5061</v>
@@ -10089,7 +10086,7 @@
     </row>
     <row r="809" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A809" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B809">
         <v>101.04286</v>
@@ -10097,7 +10094,7 @@
     </row>
     <row r="810" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A810" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B810">
         <v>101.91267999999999</v>
@@ -10105,7 +10102,7 @@
     </row>
     <row r="811" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A811" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B811">
         <v>99.666300000000007</v>
@@ -10113,7 +10110,7 @@
     </row>
     <row r="812" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A812" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B812">
         <v>135.2782</v>
@@ -10121,7 +10118,7 @@
     </row>
     <row r="813" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A813" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B813">
         <v>123.94974999999999</v>
@@ -10129,7 +10126,7 @@
     </row>
     <row r="814" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A814" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B814">
         <v>382.14400000000001</v>
@@ -10137,7 +10134,7 @@
     </row>
     <row r="815" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A815" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B815">
         <v>216.81399999999999</v>
@@ -10145,7 +10142,7 @@
     </row>
     <row r="816" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A816" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B816">
         <v>173.1087</v>
@@ -10153,7 +10150,7 @@
     </row>
     <row r="817" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A817" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B817">
         <v>153.07814999999999</v>
@@ -10161,7 +10158,7 @@
     </row>
     <row r="818" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A818" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B818">
         <v>110.23233999999999</v>
@@ -10169,7 +10166,7 @@
     </row>
     <row r="819" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A819" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B819">
         <v>125.2538</v>
@@ -10177,7 +10174,7 @@
     </row>
     <row r="820" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A820" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B820">
         <v>122.08565</v>
@@ -10185,7 +10182,7 @@
     </row>
     <row r="821" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A821" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B821">
         <v>120.26864999999999</v>
@@ -10193,7 +10190,7 @@
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A822" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B822">
         <v>135.6994</v>
@@ -10201,7 +10198,7 @@
     </row>
     <row r="823" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A823" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B823">
         <v>139.63444999999999</v>
@@ -10209,7 +10206,7 @@
     </row>
     <row r="824" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A824" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B824">
         <v>132.78415000000001</v>
@@ -10217,7 +10214,7 @@
     </row>
     <row r="825" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A825" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B825">
         <v>145.78215</v>
@@ -10225,7 +10222,7 @@
     </row>
     <row r="826" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A826" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B826">
         <v>141.64060000000001</v>
@@ -10233,7 +10230,7 @@
     </row>
     <row r="827" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A827" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B827">
         <v>117.5132</v>
@@ -10241,7 +10238,7 @@
     </row>
     <row r="828" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A828" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B828">
         <v>130.09514999999999</v>
@@ -10249,7 +10246,7 @@
     </row>
     <row r="829" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A829" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B829">
         <v>140.29355000000001</v>
@@ -10257,7 +10254,7 @@
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A830" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B830">
         <v>126.26805</v>
@@ -10265,7 +10262,7 @@
     </row>
     <row r="831" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A831" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B831">
         <v>113.66332</v>
@@ -10273,7 +10270,7 @@
     </row>
     <row r="832" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A832" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B832">
         <v>115.7244</v>
@@ -10281,7 +10278,7 @@
     </row>
     <row r="833" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A833" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B833">
         <v>109.50022</v>
@@ -10289,7 +10286,7 @@
     </row>
     <row r="834" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A834" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B834">
         <v>138.95314999999999</v>
@@ -10297,7 +10294,7 @@
     </row>
     <row r="835" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A835" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B835">
         <v>554.9</v>
@@ -10305,7 +10302,7 @@
     </row>
     <row r="836" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A836" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B836">
         <v>192.21745000000001</v>
@@ -10313,7 +10310,7 @@
     </row>
     <row r="837" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A837" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B837">
         <v>86.117360000000005</v>
@@ -10321,7 +10318,7 @@
     </row>
     <row r="838" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A838" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B838">
         <v>81.681920000000005</v>
@@ -10329,7 +10326,7 @@
     </row>
     <row r="839" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A839" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B839">
         <v>71.931520000000006</v>
@@ -10337,7 +10334,7 @@
     </row>
     <row r="840" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A840" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B840">
         <v>66.112880000000004</v>
@@ -10345,7 +10342,7 @@
     </row>
     <row r="841" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A841" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B841">
         <v>70.040080000000003</v>
@@ -10353,7 +10350,7 @@
     </row>
     <row r="842" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A842" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B842">
         <v>65.858980000000003</v>
@@ -10361,7 +10358,7 @@
     </row>
     <row r="843" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A843" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B843">
         <v>102.09614000000001</v>
@@ -10369,7 +10366,7 @@
     </row>
     <row r="844" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A844" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B844">
         <v>95.129559999999998</v>
@@ -10377,7 +10374,7 @@
     </row>
     <row r="845" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A845" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B845">
         <v>111.43894</v>
@@ -10385,7 +10382,7 @@
     </row>
     <row r="846" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A846" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B846">
         <v>104.63838</v>
@@ -10393,7 +10390,7 @@
     </row>
     <row r="847" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A847" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B847">
         <v>93.386719999999997</v>
@@ -10401,7 +10398,7 @@
     </row>
     <row r="848" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A848" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B848">
         <v>138.49684999999999</v>
@@ -10409,7 +10406,7 @@
     </row>
     <row r="849" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A849" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B849">
         <v>93.977580000000003</v>
@@ -10417,7 +10414,7 @@
     </row>
     <row r="850" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A850" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B850">
         <v>112.53077999999999</v>
@@ -10425,7 +10422,7 @@
     </row>
     <row r="851" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A851" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B851">
         <v>103.58486000000001</v>
@@ -10433,7 +10430,7 @@
     </row>
     <row r="852" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A852" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B852">
         <v>127.1673</v>
@@ -10441,7 +10438,7 @@
     </row>
     <row r="853" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A853" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B853">
         <v>72.11618</v>
@@ -10449,7 +10446,7 @@
     </row>
     <row r="854" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A854" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B854">
         <v>123.88695</v>
@@ -10457,7 +10454,7 @@
     </row>
     <row r="855" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A855" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B855">
         <v>117.3544</v>
@@ -10465,7 +10462,7 @@
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A856" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B856">
         <v>138.79325</v>
@@ -10473,7 +10470,7 @@
     </row>
     <row r="857" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A857" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B857">
         <v>229.6</v>
@@ -10481,7 +10478,7 @@
     </row>
     <row r="858" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A858" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B858">
         <v>125.71935000000001</v>
@@ -10489,7 +10486,7 @@
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A859" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B859">
         <v>132.74870000000001</v>
@@ -10497,7 +10494,7 @@
     </row>
     <row r="860" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A860" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B860">
         <v>155.32409999999999</v>
@@ -10505,7 +10502,7 @@
     </row>
     <row r="861" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A861" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B861">
         <v>106.48254</v>
@@ -10513,7 +10510,7 @@
     </row>
     <row r="862" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A862" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B862">
         <v>136.35059999999999</v>
@@ -10521,7 +10518,7 @@
     </row>
     <row r="863" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A863" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B863">
         <v>110.56108</v>
@@ -10529,7 +10526,7 @@
     </row>
     <row r="864" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A864" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B864">
         <v>150.37575000000001</v>
@@ -10537,7 +10534,7 @@
     </row>
     <row r="865" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A865" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B865">
         <v>145.07945000000001</v>
@@ -10545,7 +10542,7 @@
     </row>
     <row r="866" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A866" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B866">
         <v>136.0985</v>
@@ -10553,7 +10550,7 @@
     </row>
     <row r="867" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A867" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B867">
         <v>135.09444999999999</v>
@@ -10561,7 +10558,7 @@
     </row>
     <row r="868" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A868" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B868">
         <v>137.71295000000001</v>
@@ -10569,7 +10566,7 @@
     </row>
     <row r="869" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A869" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B869">
         <v>135.761</v>
@@ -10577,7 +10574,7 @@
     </row>
     <row r="870" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A870" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B870">
         <v>109.15940000000001</v>
@@ -10585,7 +10582,7 @@
     </row>
     <row r="871" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A871" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B871">
         <v>130.58715000000001</v>
@@ -10593,7 +10590,7 @@
     </row>
     <row r="872" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A872" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B872">
         <v>101.80058</v>
@@ -10601,7 +10598,7 @@
     </row>
     <row r="873" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A873" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B873">
         <v>141.86359999999999</v>
@@ -10609,7 +10606,7 @@
     </row>
     <row r="874" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A874" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B874">
         <v>144.75845000000001</v>
@@ -10617,7 +10614,7 @@
     </row>
     <row r="875" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A875" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B875">
         <v>128.29785000000001</v>
@@ -10625,7 +10622,7 @@
     </row>
     <row r="876" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A876" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B876">
         <v>141.78305</v>
@@ -10633,7 +10630,7 @@
     </row>
     <row r="877" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A877" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B877">
         <v>134.23750000000001</v>
@@ -10641,7 +10638,7 @@
     </row>
     <row r="878" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A878" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B878">
         <v>35.31617</v>
@@ -10649,7 +10646,7 @@
     </row>
     <row r="879" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A879" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B879">
         <v>75.841480000000004</v>
@@ -10657,7 +10654,7 @@
     </row>
     <row r="880" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A880" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B880">
         <v>75.238759999999999</v>
@@ -10665,7 +10662,7 @@
     </row>
     <row r="881" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A881" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B881">
         <v>66.293400000000005</v>
@@ -10673,7 +10670,7 @@
     </row>
     <row r="882" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A882" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B882">
         <v>94.152979999999999</v>
@@ -10681,7 +10678,7 @@
     </row>
     <row r="883" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A883" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B883">
         <v>79.8703</v>
@@ -10689,7 +10686,7 @@
     </row>
     <row r="884" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A884" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B884">
         <v>74.948639999999997</v>
@@ -10697,7 +10694,7 @@
     </row>
     <row r="885" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A885" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B885">
         <v>110.75915999999999</v>
@@ -10705,7 +10702,7 @@
     </row>
     <row r="886" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A886" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B886">
         <v>87.664580000000001</v>
@@ -10713,7 +10710,7 @@
     </row>
     <row r="887" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A887" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B887">
         <v>81.055440000000004</v>
@@ -10721,7 +10718,7 @@
     </row>
     <row r="888" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A888" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B888">
         <v>119.28802</v>
@@ -10729,7 +10726,7 @@
     </row>
     <row r="889" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A889" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B889">
         <v>116.63872000000001</v>
@@ -10737,7 +10734,7 @@
     </row>
     <row r="890" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A890" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B890">
         <v>118.77906</v>
@@ -10745,7 +10742,7 @@
     </row>
     <row r="891" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A891" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B891">
         <v>117.18226</v>
@@ -10753,7 +10750,7 @@
     </row>
     <row r="892" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A892" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B892">
         <v>120.19880000000001</v>
@@ -10761,7 +10758,7 @@
     </row>
     <row r="893" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A893" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B893">
         <v>129.6335</v>
@@ -10769,7 +10766,7 @@
     </row>
     <row r="894" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A894" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B894">
         <v>87.353300000000004</v>
@@ -10777,7 +10774,7 @@
     </row>
     <row r="895" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A895" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B895">
         <v>100.35796000000001</v>
@@ -10785,7 +10782,7 @@
     </row>
     <row r="896" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A896" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B896">
         <v>123.74995</v>
@@ -10793,7 +10790,7 @@
     </row>
     <row r="897" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A897" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B897">
         <v>145.25255000000001</v>
@@ -10801,7 +10798,7 @@
     </row>
     <row r="898" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A898" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B898">
         <v>499.702</v>
@@ -10809,7 +10806,7 @@
     </row>
     <row r="899" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A899" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B899">
         <v>123.86435</v>
@@ -10817,7 +10814,7 @@
     </row>
     <row r="900" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A900" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B900">
         <v>146.20820000000001</v>
@@ -10825,7 +10822,7 @@
     </row>
     <row r="901" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A901" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B901">
         <v>121.24835</v>
@@ -10833,7 +10830,7 @@
     </row>
     <row r="902" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A902" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B902">
         <v>112.55104</v>
@@ -10841,7 +10838,7 @@
     </row>
     <row r="903" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A903" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B903">
         <v>134.25139999999999</v>
@@ -10849,7 +10846,7 @@
     </row>
     <row r="904" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A904" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B904">
         <v>141.65334999999999</v>
@@ -10857,7 +10854,7 @@
     </row>
     <row r="905" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A905" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B905">
         <v>117.49198</v>
@@ -10865,7 +10862,7 @@
     </row>
     <row r="906" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A906" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B906">
         <v>148.59684999999999</v>
@@ -10873,7 +10870,7 @@
     </row>
     <row r="907" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A907" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B907">
         <v>151.80850000000001</v>
@@ -10881,7 +10878,7 @@
     </row>
     <row r="908" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A908" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B908">
         <v>100.67892000000001</v>
@@ -10889,7 +10886,7 @@
     </row>
     <row r="909" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A909" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B909">
         <v>132.05770000000001</v>
@@ -10897,7 +10894,7 @@
     </row>
     <row r="910" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A910" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B910">
         <v>113.83242</v>
@@ -10905,7 +10902,7 @@
     </row>
     <row r="911" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A911" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B911">
         <v>147.52979999999999</v>
@@ -10913,7 +10910,7 @@
     </row>
     <row r="912" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A912" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B912">
         <v>135.5264</v>
@@ -10921,7 +10918,7 @@
     </row>
     <row r="913" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A913" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B913">
         <v>156.92054999999999</v>
@@ -10929,7 +10926,7 @@
     </row>
     <row r="914" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A914" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B914">
         <v>127.79434999999999</v>
@@ -10937,7 +10934,7 @@
     </row>
     <row r="915" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A915" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B915">
         <v>132.76830000000001</v>
@@ -10945,7 +10942,7 @@
     </row>
     <row r="916" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A916" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B916">
         <v>120.5078</v>
@@ -10953,7 +10950,7 @@
     </row>
     <row r="917" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A917" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B917">
         <v>125.6947</v>
@@ -10961,7 +10958,7 @@
     </row>
     <row r="918" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A918" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B918">
         <v>133.78505000000001</v>
@@ -10969,7 +10966,7 @@
     </row>
     <row r="919" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A919" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B919">
         <v>323.12599999999998</v>
@@ -10977,7 +10974,7 @@
     </row>
     <row r="920" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A920" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B920">
         <v>94.812700000000007</v>
@@ -10985,7 +10982,7 @@
     </row>
     <row r="921" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A921" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B921">
         <v>95.037480000000002</v>
@@ -10993,7 +10990,7 @@
     </row>
     <row r="922" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A922" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B922">
         <v>83.937839999999994</v>
@@ -11001,7 +10998,7 @@
     </row>
     <row r="923" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A923" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B923">
         <v>71.756100000000004</v>
@@ -11009,7 +11006,7 @@
     </row>
     <row r="924" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A924" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B924">
         <v>93.002120000000005</v>
@@ -11017,7 +11014,7 @@
     </row>
     <row r="925" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A925" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B925">
         <v>73.929060000000007</v>
@@ -11025,7 +11022,7 @@
     </row>
     <row r="926" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A926" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B926">
         <v>84.830759999999998</v>
@@ -11033,7 +11030,7 @@
     </row>
     <row r="927" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A927" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B927">
         <v>67.629840000000002</v>
@@ -11041,7 +11038,7 @@
     </row>
     <row r="928" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A928" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B928">
         <v>75.922020000000003</v>
@@ -11049,7 +11046,7 @@
     </row>
     <row r="929" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A929" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B929">
         <v>78.927379999999999</v>
@@ -11057,7 +11054,7 @@
     </row>
     <row r="930" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A930" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B930">
         <v>77.910979999999995</v>
@@ -11065,7 +11062,7 @@
     </row>
     <row r="931" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A931" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B931">
         <v>94.899619999999999</v>
@@ -11073,7 +11070,7 @@
     </row>
     <row r="932" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A932" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B932">
         <v>105.14348</v>
@@ -11081,7 +11078,7 @@
     </row>
     <row r="933" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A933" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B933">
         <v>108.13736</v>
@@ -11089,7 +11086,7 @@
     </row>
     <row r="934" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A934" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B934">
         <v>90.578220000000002</v>
@@ -11097,7 +11094,7 @@
     </row>
     <row r="935" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A935" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B935">
         <v>108.91902</v>
@@ -11105,7 +11102,7 @@
     </row>
     <row r="936" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A936" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B936">
         <v>100.38974</v>
@@ -11113,7 +11110,7 @@
     </row>
     <row r="937" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A937" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B937">
         <v>87.950519999999997</v>
@@ -11121,7 +11118,7 @@
     </row>
     <row r="938" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A938" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B938">
         <v>111.20146</v>
@@ -11129,7 +11126,7 @@
     </row>
     <row r="939" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A939" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B939">
         <v>100.02316</v>
@@ -11137,7 +11134,7 @@
     </row>
     <row r="940" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A940" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B940">
         <v>299.505</v>
@@ -11145,7 +11142,7 @@
     </row>
     <row r="941" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A941" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B941">
         <v>135.21170000000001</v>
@@ -11153,7 +11150,7 @@
     </row>
     <row r="942" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A942" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B942">
         <v>95.115480000000005</v>
@@ -11161,7 +11158,7 @@
     </row>
     <row r="943" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A943" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B943">
         <v>95.543760000000006</v>
@@ -11169,7 +11166,7 @@
     </row>
     <row r="944" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A944" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B944">
         <v>124.1849</v>
@@ -11177,7 +11174,7 @@
     </row>
     <row r="945" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A945" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B945">
         <v>119.26992</v>
@@ -11185,7 +11182,7 @@
     </row>
     <row r="946" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A946" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B946">
         <v>151.55850000000001</v>
@@ -11193,7 +11190,7 @@
     </row>
     <row r="947" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A947" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B947">
         <v>149.12129999999999</v>
@@ -11201,7 +11198,7 @@
     </row>
     <row r="948" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A948" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B948">
         <v>132.01845</v>
@@ -11209,7 +11206,7 @@
     </row>
     <row r="949" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A949" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B949">
         <v>149.60034999999999</v>
@@ -11217,7 +11214,7 @@
     </row>
     <row r="950" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A950" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B950">
         <v>105.19422</v>
@@ -11225,7 +11222,7 @@
     </row>
     <row r="951" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A951" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B951">
         <v>164.5462</v>
@@ -11233,7 +11230,7 @@
     </row>
     <row r="952" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A952" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B952">
         <v>105.2324</v>
@@ -11241,7 +11238,7 @@
     </row>
     <row r="953" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A953" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B953">
         <v>161.34344999999999</v>
@@ -11249,7 +11246,7 @@
     </row>
     <row r="954" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A954" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B954">
         <v>114.70623999999999</v>
@@ -11257,7 +11254,7 @@
     </row>
     <row r="955" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A955" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B955">
         <v>150.49535</v>
@@ -11265,7 +11262,7 @@
     </row>
     <row r="956" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A956" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B956">
         <v>141.43145000000001</v>
@@ -11273,7 +11270,7 @@
     </row>
     <row r="957" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A957" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B957">
         <v>110.98779999999999</v>
@@ -11281,7 +11278,7 @@
     </row>
     <row r="958" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A958" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B958">
         <v>130.12264999999999</v>
@@ -11289,7 +11286,7 @@
     </row>
     <row r="959" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A959" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B959">
         <v>128.22174999999999</v>
@@ -11297,7 +11294,7 @@
     </row>
     <row r="960" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A960" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B960">
         <v>112.6026</v>
@@ -11305,7 +11302,7 @@
     </row>
     <row r="961" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A961" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B961">
         <v>545.29999999999995</v>
@@ -11313,7 +11310,7 @@
     </row>
     <row r="962" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A962" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B962">
         <v>79.155799999999999</v>
@@ -11321,7 +11318,7 @@
     </row>
     <row r="963" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A963" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B963">
         <v>82.980900000000005</v>
@@ -11329,7 +11326,7 @@
     </row>
     <row r="964" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A964" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B964">
         <v>104.24068</v>
@@ -11337,7 +11334,7 @@
     </row>
     <row r="965" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A965" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B965">
         <v>85.710099999999997</v>
@@ -11345,7 +11342,7 @@
     </row>
     <row r="966" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A966" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B966">
         <v>93.670599999999993</v>
@@ -11353,7 +11350,7 @@
     </row>
     <row r="967" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A967" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B967">
         <v>62.909019999999998</v>
@@ -11361,7 +11358,7 @@
     </row>
     <row r="968" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A968" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B968">
         <v>103.25802</v>
@@ -11369,7 +11366,7 @@
     </row>
     <row r="969" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A969" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B969">
         <v>102.67543999999999</v>
@@ -11377,7 +11374,7 @@
     </row>
     <row r="970" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A970" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B970">
         <v>111.70544</v>
@@ -11385,7 +11382,7 @@
     </row>
     <row r="971" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A971" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B971">
         <v>86.358180000000004</v>
@@ -11393,7 +11390,7 @@
     </row>
     <row r="972" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A972" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B972">
         <v>89.304919999999996</v>
@@ -11401,7 +11398,7 @@
     </row>
     <row r="973" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A973" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B973">
         <v>105.2963</v>
@@ -11409,7 +11406,7 @@
     </row>
     <row r="974" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A974" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B974">
         <v>140.27985000000001</v>
@@ -11417,7 +11414,7 @@
     </row>
     <row r="975" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A975" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B975">
         <v>116.44768000000001</v>
@@ -11425,7 +11422,7 @@
     </row>
     <row r="976" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A976" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B976">
         <v>100.40608</v>
@@ -11433,7 +11430,7 @@
     </row>
     <row r="977" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A977" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B977">
         <v>111.33616000000001</v>
@@ -11441,7 +11438,7 @@
     </row>
     <row r="978" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A978" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B978">
         <v>108.46316</v>
@@ -11449,7 +11446,7 @@
     </row>
     <row r="979" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A979" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B979">
         <v>105.15272</v>
@@ -11457,7 +11454,7 @@
     </row>
     <row r="980" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A980" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B980">
         <v>118.6006</v>
@@ -11465,7 +11462,7 @@
     </row>
     <row r="981" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A981" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B981">
         <v>105.3707</v>
@@ -11473,7 +11470,7 @@
     </row>
     <row r="982" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A982" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B982">
         <v>432.24400000000003</v>
@@ -11481,7 +11478,7 @@
     </row>
     <row r="983" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A983" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B983">
         <v>127.5997</v>
@@ -11489,7 +11486,7 @@
     </row>
     <row r="984" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A984" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B984">
         <v>127.37255</v>
@@ -11497,7 +11494,7 @@
     </row>
     <row r="985" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A985" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B985">
         <v>96.233680000000007</v>
@@ -11505,7 +11502,7 @@
     </row>
     <row r="986" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A986" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B986">
         <v>101.52956</v>
@@ -11513,7 +11510,7 @@
     </row>
     <row r="987" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A987" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B987">
         <v>122.24509999999999</v>
@@ -11521,7 +11518,7 @@
     </row>
     <row r="988" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A988" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B988">
         <v>132.03540000000001</v>
@@ -11529,7 +11526,7 @@
     </row>
     <row r="989" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A989" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B989">
         <v>116.89812000000001</v>
@@ -11537,7 +11534,7 @@
     </row>
     <row r="990" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A990" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B990">
         <v>125.84245</v>
@@ -11545,7 +11542,7 @@
     </row>
     <row r="991" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A991" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B991">
         <v>133.47114999999999</v>
@@ -11553,7 +11550,7 @@
     </row>
     <row r="992" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A992" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B992">
         <v>125.11735</v>
@@ -11561,7 +11558,7 @@
     </row>
     <row r="993" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A993" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B993">
         <v>119.53778</v>
@@ -11569,7 +11566,7 @@
     </row>
     <row r="994" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A994" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B994">
         <v>132.77945</v>
@@ -11577,7 +11574,7 @@
     </row>
     <row r="995" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A995" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B995">
         <v>85.885019999999997</v>
@@ -11585,7 +11582,7 @@
     </row>
     <row r="996" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A996" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B996">
         <v>108.65891999999999</v>
@@ -11593,7 +11590,7 @@
     </row>
     <row r="997" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A997" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B997">
         <v>96.75752</v>
@@ -11601,7 +11598,7 @@
     </row>
     <row r="998" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A998" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B998">
         <v>75.703440000000001</v>
@@ -11609,7 +11606,7 @@
     </row>
     <row r="999" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A999" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B999">
         <v>129.69264999999999</v>
@@ -11617,7 +11614,7 @@
     </row>
     <row r="1000" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1000" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B1000">
         <v>156.0121</v>
@@ -11625,7 +11622,7 @@
     </row>
     <row r="1001" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1001" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B1001">
         <v>176.94794999999999</v>
@@ -11633,7 +11630,7 @@
     </row>
     <row r="1002" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1002" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B1002">
         <v>138.59725</v>
@@ -11641,7 +11638,7 @@
     </row>
     <row r="1003" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1003" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B1003">
         <v>747.3</v>
@@ -11649,7 +11646,7 @@
     </row>
     <row r="1004" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1004" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B1004">
         <v>95.300060000000002</v>
@@ -11657,7 +11654,7 @@
     </row>
     <row r="1005" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1005" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B1005">
         <v>63.202440000000003</v>
@@ -11665,7 +11662,7 @@
     </row>
     <row r="1006" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1006" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B1006">
         <v>88.1327</v>
@@ -11673,7 +11670,7 @@
     </row>
     <row r="1007" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1007" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B1007">
         <v>88.549019999999999</v>
@@ -11681,7 +11678,7 @@
     </row>
     <row r="1008" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1008" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B1008">
         <v>83.732939999999999</v>
@@ -11689,7 +11686,7 @@
     </row>
     <row r="1009" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1009" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B1009">
         <v>86.342399999999998</v>
@@ -11697,7 +11694,7 @@
     </row>
     <row r="1010" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1010" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B1010">
         <v>92.340239999999994</v>
@@ -11705,7 +11702,7 @@
     </row>
     <row r="1011" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1011" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B1011">
         <v>73.764480000000006</v>
@@ -11713,7 +11710,7 @@
     </row>
     <row r="1012" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1012" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B1012">
         <v>94.117000000000004</v>
@@ -11721,7 +11718,7 @@
     </row>
     <row r="1013" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1013" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B1013">
         <v>102.1827</v>
@@ -11729,7 +11726,7 @@
     </row>
     <row r="1014" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1014" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B1014">
         <v>68.705359999999999</v>
@@ -11737,7 +11734,7 @@
     </row>
     <row r="1015" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1015" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B1015">
         <v>124.66245000000001</v>
@@ -11745,7 +11742,7 @@
     </row>
     <row r="1016" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1016" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B1016">
         <v>112.53774</v>
@@ -11753,7 +11750,7 @@
     </row>
     <row r="1017" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1017" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B1017">
         <v>80.713419999999999</v>
@@ -11761,7 +11758,7 @@
     </row>
     <row r="1018" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1018" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B1018">
         <v>82.636480000000006</v>
@@ -11769,7 +11766,7 @@
     </row>
     <row r="1019" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1019" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B1019">
         <v>122.58975</v>
@@ -11777,7 +11774,7 @@
     </row>
     <row r="1020" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1020" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B1020">
         <v>106.16718</v>
@@ -11785,7 +11782,7 @@
     </row>
     <row r="1021" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1021" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B1021">
         <v>85.396960000000007</v>
@@ -11793,7 +11790,7 @@
     </row>
     <row r="1022" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1022" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B1022">
         <v>119.70018</v>
@@ -11801,7 +11798,7 @@
     </row>
     <row r="1023" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1023" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B1023">
         <v>107.51349999999999</v>
@@ -11809,7 +11806,7 @@
     </row>
     <row r="1024" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1024" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B1024">
         <v>562.70000000000005</v>
@@ -11817,7 +11814,7 @@
     </row>
     <row r="1025" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1025" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B1025">
         <v>112.27488</v>
@@ -11825,7 +11822,7 @@
     </row>
     <row r="1026" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1026" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B1026">
         <v>95.932739999999995</v>
@@ -11833,7 +11830,7 @@
     </row>
     <row r="1027" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1027" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B1027">
         <v>113.82938</v>
@@ -11841,7 +11838,7 @@
     </row>
     <row r="1028" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1028" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B1028">
         <v>106.66589999999999</v>
@@ -11849,7 +11846,7 @@
     </row>
     <row r="1029" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1029" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B1029">
         <v>135.52395000000001</v>
@@ -11857,7 +11854,7 @@
     </row>
     <row r="1030" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1030" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B1030">
         <v>120.3505</v>
@@ -11865,7 +11862,7 @@
     </row>
     <row r="1031" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1031" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B1031">
         <v>111.85711999999999</v>
@@ -11873,7 +11870,7 @@
     </row>
     <row r="1032" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1032" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B1032">
         <v>145.63425000000001</v>
@@ -11881,7 +11878,7 @@
     </row>
     <row r="1033" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1033" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B1033">
         <v>132.2979</v>
@@ -11889,7 +11886,7 @@
     </row>
     <row r="1034" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1034" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B1034">
         <v>134.6455</v>
@@ -11897,7 +11894,7 @@
     </row>
     <row r="1035" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1035" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B1035">
         <v>134.3931</v>
@@ -11905,7 +11902,7 @@
     </row>
     <row r="1036" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1036" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B1036">
         <v>129.17234999999999</v>
@@ -11913,7 +11910,7 @@
     </row>
     <row r="1037" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1037" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B1037">
         <v>131.80525</v>
@@ -11921,7 +11918,7 @@
     </row>
     <row r="1038" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1038" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B1038">
         <v>132.3434</v>
@@ -11929,7 +11926,7 @@
     </row>
     <row r="1039" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1039" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B1039">
         <v>135.4058</v>
@@ -11937,7 +11934,7 @@
     </row>
     <row r="1040" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1040" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B1040">
         <v>132.94725</v>
@@ -11945,7 +11942,7 @@
     </row>
     <row r="1041" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1041" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B1041">
         <v>126.0181</v>
@@ -11953,7 +11950,7 @@
     </row>
     <row r="1042" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1042" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B1042">
         <v>155.36590000000001</v>
@@ -11961,7 +11958,7 @@
     </row>
     <row r="1043" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1043" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B1043">
         <v>137.64230000000001</v>
@@ -11969,7 +11966,7 @@
     </row>
     <row r="1044" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1044" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B1044">
         <v>143.18225000000001</v>
@@ -11977,7 +11974,7 @@
     </row>
     <row r="1045" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1045" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B1045">
         <v>777.4</v>
@@ -11985,7 +11982,7 @@
     </row>
     <row r="1046" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1046" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B1046">
         <v>170.86165</v>
@@ -11993,7 +11990,7 @@
     </row>
     <row r="1047" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1047" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B1047">
         <v>100.65028</v>
@@ -12001,7 +11998,7 @@
     </row>
     <row r="1048" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1048" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B1048">
         <v>92.304659999999998</v>
@@ -12009,7 +12006,7 @@
     </row>
     <row r="1049" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1049" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B1049">
         <v>89.16216</v>
@@ -12017,7 +12014,7 @@
     </row>
     <row r="1050" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1050" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B1050">
         <v>79.828040000000001</v>
@@ -12025,7 +12022,7 @@
     </row>
     <row r="1051" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1051" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B1051">
         <v>74.577659999999995</v>
@@ -12033,7 +12030,7 @@
     </row>
     <row r="1052" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1052" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B1052">
         <v>88.021739999999994</v>
@@ -12041,7 +12038,7 @@
     </row>
     <row r="1053" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1053" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B1053">
         <v>79.148039999999995</v>
@@ -12049,7 +12046,7 @@
     </row>
     <row r="1054" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1054" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B1054">
         <v>97.121359999999996</v>
@@ -12057,7 +12054,7 @@
     </row>
     <row r="1055" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1055" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B1055">
         <v>83.634839999999997</v>
@@ -12065,7 +12062,7 @@
     </row>
     <row r="1056" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1056" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B1056">
         <v>85.653840000000002</v>
@@ -12073,7 +12070,7 @@
     </row>
     <row r="1057" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1057" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B1057">
         <v>130.79644999999999</v>
@@ -12081,7 +12078,7 @@
     </row>
     <row r="1058" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1058" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B1058">
         <v>92.436760000000007</v>
@@ -12089,7 +12086,7 @@
     </row>
     <row r="1059" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1059" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B1059">
         <v>122.09665</v>
@@ -12097,7 +12094,7 @@
     </row>
     <row r="1060" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1060" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B1060">
         <v>92.889380000000003</v>
@@ -12105,7 +12102,7 @@
     </row>
     <row r="1061" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1061" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B1061">
         <v>103.46306</v>
@@ -12113,7 +12110,7 @@
     </row>
     <row r="1062" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1062" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B1062">
         <v>97.912099999999995</v>
@@ -12121,7 +12118,7 @@
     </row>
     <row r="1063" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1063" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B1063">
         <v>123.68474999999999</v>
@@ -12129,7 +12126,7 @@
     </row>
     <row r="1064" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1064" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B1064">
         <v>122.24724999999999</v>
@@ -12137,7 +12134,7 @@
     </row>
     <row r="1065" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1065" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B1065">
         <v>94.478740000000002</v>
@@ -12145,7 +12142,7 @@
     </row>
     <row r="1066" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1066" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B1066">
         <v>419.8</v>
@@ -12153,7 +12150,7 @@
     </row>
     <row r="1067" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1067" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B1067">
         <v>228.012</v>
@@ -12161,7 +12158,7 @@
     </row>
     <row r="1068" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1068" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B1068">
         <v>150.65905000000001</v>
@@ -12169,7 +12166,7 @@
     </row>
     <row r="1069" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1069" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B1069">
         <v>177.22495000000001</v>
@@ -12177,7 +12174,7 @@
     </row>
     <row r="1070" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1070" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B1070">
         <v>143.08645000000001</v>
@@ -12185,7 +12182,7 @@
     </row>
     <row r="1071" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1071" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B1071">
         <v>138.8964</v>
@@ -12193,7 +12190,7 @@
     </row>
     <row r="1072" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1072" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B1072">
         <v>129.55725000000001</v>
@@ -12201,7 +12198,7 @@
     </row>
     <row r="1073" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1073" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B1073">
         <v>137.13995</v>
@@ -12209,7 +12206,7 @@
     </row>
     <row r="1074" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1074" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B1074">
         <v>132.78299999999999</v>
@@ -12217,7 +12214,7 @@
     </row>
     <row r="1075" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1075" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B1075">
         <v>123.77355</v>
@@ -12225,7 +12222,7 @@
     </row>
     <row r="1076" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1076" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B1076">
         <v>141.37805</v>
@@ -12233,7 +12230,7 @@
     </row>
     <row r="1077" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1077" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B1077">
         <v>138.90950000000001</v>
@@ -12241,7 +12238,7 @@
     </row>
     <row r="1078" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1078" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B1078">
         <v>137.31475</v>
@@ -12249,7 +12246,7 @@
     </row>
     <row r="1079" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1079" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B1079">
         <v>110.62052</v>
@@ -12257,7 +12254,7 @@
     </row>
     <row r="1080" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1080" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B1080">
         <v>103.2415</v>
@@ -12265,7 +12262,7 @@
     </row>
     <row r="1081" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1081" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B1081">
         <v>106.28278</v>
@@ -12273,7 +12270,7 @@
     </row>
     <row r="1082" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1082" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B1082">
         <v>83.3048</v>
@@ -12281,7 +12278,7 @@
     </row>
     <row r="1083" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1083" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B1083">
         <v>116.52708</v>
@@ -12289,7 +12286,7 @@
     </row>
     <row r="1084" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1084" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B1084">
         <v>109.96368</v>
@@ -12297,7 +12294,7 @@
     </row>
     <row r="1085" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1085" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B1085">
         <v>116.4402</v>
@@ -12305,7 +12302,7 @@
     </row>
     <row r="1086" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1086" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B1086">
         <v>116.16</v>
@@ -12313,7 +12310,7 @@
     </row>
     <row r="1087" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1087" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B1087">
         <v>620.20000000000005</v>
@@ -12321,7 +12318,7 @@
     </row>
     <row r="1088" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1088" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B1088">
         <v>111.99021999999999</v>
@@ -12329,7 +12326,7 @@
     </row>
     <row r="1089" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1089" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B1089">
         <v>64.988100000000003</v>
@@ -12337,7 +12334,7 @@
     </row>
     <row r="1090" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1090" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B1090">
         <v>67.143659999999997</v>
@@ -12345,7 +12342,7 @@
     </row>
     <row r="1091" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1091" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B1091">
         <v>71.029719999999998</v>
@@ -12353,7 +12350,7 @@
     </row>
     <row r="1092" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1092" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B1092">
         <v>74.019660000000002</v>
@@ -12361,7 +12358,7 @@
     </row>
     <row r="1093" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1093" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B1093">
         <v>73.09402</v>
@@ -12369,7 +12366,7 @@
     </row>
     <row r="1094" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1094" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B1094">
         <v>83.132819999999995</v>
@@ -12377,7 +12374,7 @@
     </row>
     <row r="1095" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1095" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B1095">
         <v>89.99306</v>
@@ -12385,7 +12382,7 @@
     </row>
     <row r="1096" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1096" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B1096">
         <v>82.337239999999994</v>
@@ -12393,7 +12390,7 @@
     </row>
     <row r="1097" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1097" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B1097">
         <v>98.765140000000002</v>
@@ -12401,7 +12398,7 @@
     </row>
     <row r="1098" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1098" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B1098">
         <v>99.537459999999996</v>
@@ -12409,7 +12406,7 @@
     </row>
     <row r="1099" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1099" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B1099">
         <v>120.75305</v>
@@ -12417,7 +12414,7 @@
     </row>
     <row r="1100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1100" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B1100">
         <v>101.40116</v>
@@ -12425,7 +12422,7 @@
     </row>
     <row r="1101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1101" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B1101">
         <v>115.91526</v>
@@ -12433,7 +12430,7 @@
     </row>
     <row r="1102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1102" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B1102">
         <v>101.60494</v>
@@ -12441,7 +12438,7 @@
     </row>
     <row r="1103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1103" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B1103">
         <v>100.5701</v>
@@ -12449,7 +12446,7 @@
     </row>
     <row r="1104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1104" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B1104">
         <v>115.24639999999999</v>
@@ -12457,7 +12454,7 @@
     </row>
     <row r="1105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1105" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B1105">
         <v>104.53176000000001</v>
@@ -12465,7 +12462,7 @@
     </row>
     <row r="1106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1106" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B1106">
         <v>97.104519999999994</v>
@@ -12473,7 +12470,7 @@
     </row>
     <row r="1107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1107" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B1107">
         <v>103.99884</v>
@@ -12481,7 +12478,7 @@
     </row>
     <row r="1108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1108" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B1108">
         <v>548.1</v>
@@ -12489,7 +12486,7 @@
     </row>
     <row r="1109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1109" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B1109">
         <v>226.49199999999999</v>
@@ -12497,7 +12494,7 @@
     </row>
     <row r="1110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1110" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B1110">
         <v>150.89605</v>
@@ -12505,7 +12502,7 @@
     </row>
     <row r="1111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1111" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B1111">
         <v>124.61105000000001</v>
@@ -12513,7 +12510,7 @@
     </row>
     <row r="1112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1112" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B1112">
         <v>120.83385</v>
@@ -12521,7 +12518,7 @@
     </row>
     <row r="1113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1113" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B1113">
         <v>130.04265000000001</v>
@@ -12529,7 +12526,7 @@
     </row>
     <row r="1114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1114" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B1114">
         <v>143.33494999999999</v>
@@ -12537,7 +12534,7 @@
     </row>
     <row r="1115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1115" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B1115">
         <v>122.88724999999999</v>
@@ -12545,7 +12542,7 @@
     </row>
     <row r="1116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1116" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B1116">
         <v>152.88475</v>
@@ -12553,7 +12550,7 @@
     </row>
     <row r="1117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1117" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B1117">
         <v>133.58455000000001</v>
@@ -12561,7 +12558,7 @@
     </row>
     <row r="1118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1118" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B1118">
         <v>139.84434999999999</v>
@@ -12569,7 +12566,7 @@
     </row>
     <row r="1119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1119" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B1119">
         <v>127.80934999999999</v>
@@ -12577,7 +12574,7 @@
     </row>
     <row r="1120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1120" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B1120">
         <v>131.68610000000001</v>
@@ -12585,7 +12582,7 @@
     </row>
     <row r="1121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1121" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B1121">
         <v>144.5531</v>
@@ -12593,7 +12590,7 @@
     </row>
     <row r="1122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1122" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B1122">
         <v>144.48984999999999</v>
@@ -12601,7 +12598,7 @@
     </row>
     <row r="1123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1123" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B1123">
         <v>122.25985</v>
@@ -12609,7 +12606,7 @@
     </row>
     <row r="1124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1124" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B1124">
         <v>128.22274999999999</v>
@@ -12617,7 +12614,7 @@
     </row>
     <row r="1125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1125" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B1125">
         <v>125.55295</v>
@@ -12625,7 +12622,7 @@
     </row>
     <row r="1126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1126" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B1126">
         <v>140.90545</v>
@@ -12633,7 +12630,7 @@
     </row>
     <row r="1127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1127" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B1127">
         <v>138.34375</v>
@@ -12641,7 +12638,7 @@
     </row>
     <row r="1128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1128" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B1128">
         <v>121.52785</v>
@@ -12649,7 +12646,7 @@
     </row>
     <row r="1129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1129" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B1129">
         <v>484.9</v>
@@ -12657,7 +12654,7 @@
     </row>
     <row r="1130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1130" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B1130">
         <v>96.220780000000005</v>
@@ -12665,7 +12662,7 @@
     </row>
     <row r="1131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1131" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B1131">
         <v>79.788179999999997</v>
@@ -12673,7 +12670,7 @@
     </row>
     <row r="1132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1132" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B1132">
         <v>91.328379999999996</v>
@@ -12681,7 +12678,7 @@
     </row>
     <row r="1133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1133" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B1133">
         <v>91.091059999999999</v>
@@ -12689,7 +12686,7 @@
     </row>
     <row r="1134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1134" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B1134">
         <v>74.822760000000002</v>
@@ -12697,7 +12694,7 @@
     </row>
     <row r="1135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1135" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B1135">
         <v>86.810320000000004</v>
@@ -12705,7 +12702,7 @@
     </row>
     <row r="1136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1136" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B1136">
         <v>78.066119999999998</v>
@@ -12713,7 +12710,7 @@
     </row>
     <row r="1137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1137" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B1137">
         <v>105.1661</v>
@@ -12721,7 +12718,7 @@
     </row>
     <row r="1138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1138" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B1138">
         <v>99.526079999999993</v>
@@ -12729,7 +12726,7 @@
     </row>
     <row r="1139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1139" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B1139">
         <v>98.537120000000002</v>
@@ -12737,7 +12734,7 @@
     </row>
     <row r="1140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1140" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B1140">
         <v>100.37472</v>
@@ -12745,7 +12742,7 @@
     </row>
     <row r="1141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1141" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B1141">
         <v>111.35722</v>
@@ -12753,7 +12750,7 @@
     </row>
     <row r="1142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1142" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B1142">
         <v>87.626360000000005</v>
@@ -12761,7 +12758,7 @@
     </row>
     <row r="1143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1143" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B1143">
         <v>105.37560000000001</v>
@@ -12769,7 +12766,7 @@
     </row>
     <row r="1144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1144" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B1144">
         <v>121.01635</v>
@@ -12777,7 +12774,7 @@
     </row>
     <row r="1145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1145" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B1145">
         <v>98.287040000000005</v>
@@ -12785,7 +12782,7 @@
     </row>
     <row r="1146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1146" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B1146">
         <v>113.41562</v>
@@ -12793,7 +12790,7 @@
     </row>
     <row r="1147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1147" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B1147">
         <v>128.66874999999999</v>
@@ -12801,7 +12798,7 @@
     </row>
     <row r="1148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1148" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B1148">
         <v>107.14276</v>
@@ -12809,7 +12806,7 @@
     </row>
     <row r="1149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1149" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B1149">
         <v>101.3471</v>
@@ -12817,7 +12814,7 @@
     </row>
     <row r="1150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1150" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B1150">
         <v>654.5</v>
@@ -12825,7 +12822,7 @@
     </row>
     <row r="1151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1151" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B1151">
         <v>201.83744999999999</v>
@@ -12833,7 +12830,7 @@
     </row>
     <row r="1152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1152" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B1152">
         <v>138.44704999999999</v>
@@ -12841,7 +12838,7 @@
     </row>
     <row r="1153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1153" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B1153">
         <v>130.9153</v>
@@ -12849,7 +12846,7 @@
     </row>
     <row r="1154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1154" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B1154">
         <v>135.77885000000001</v>
@@ -12857,7 +12854,7 @@
     </row>
     <row r="1155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1155" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B1155">
         <v>132.22975</v>
@@ -12865,7 +12862,7 @@
     </row>
     <row r="1156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1156" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B1156">
         <v>131.8734</v>
@@ -12873,7 +12870,7 @@
     </row>
     <row r="1157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1157" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B1157">
         <v>125.67364999999999</v>
@@ -12881,7 +12878,7 @@
     </row>
     <row r="1158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1158" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B1158">
         <v>124.7655</v>
@@ -12889,7 +12886,7 @@
     </row>
     <row r="1159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1159" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B1159">
         <v>130.36510000000001</v>
@@ -12897,7 +12894,7 @@
     </row>
     <row r="1160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1160" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B1160">
         <v>134.26005000000001</v>
@@ -12905,7 +12902,7 @@
     </row>
     <row r="1161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1161" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B1161">
         <v>132.57294999999999</v>
@@ -12913,7 +12910,7 @@
     </row>
     <row r="1162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1162" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B1162">
         <v>119.87426000000001</v>
@@ -12921,7 +12918,7 @@
     </row>
     <row r="1163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1163" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B1163">
         <v>133.20124999999999</v>
@@ -12929,7 +12926,7 @@
     </row>
     <row r="1164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1164" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B1164">
         <v>126.98779999999999</v>
@@ -12937,7 +12934,7 @@
     </row>
     <row r="1165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1165" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B1165">
         <v>129.84835000000001</v>
@@ -12945,7 +12942,7 @@
     </row>
     <row r="1166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1166" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B1166">
         <v>119.77227999999999</v>
@@ -12953,7 +12950,7 @@
     </row>
     <row r="1167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1167" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B1167">
         <v>151.86584999999999</v>
@@ -12961,7 +12958,7 @@
     </row>
     <row r="1168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1168" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B1168">
         <v>110.02526</v>
@@ -12969,15 +12966,15 @@
     </row>
     <row r="1169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1169" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B1169" t="s">
-        <v>318</v>
+        <v>1050</v>
+      </c>
+      <c r="B1169">
+        <v>119.22087999999999</v>
       </c>
     </row>
     <row r="1170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1170" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B1170">
         <v>99.766819999999996</v>
@@ -12985,7 +12982,7 @@
     </row>
     <row r="1171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1171" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B1171">
         <v>360.71699999999998</v>
@@ -12993,7 +12990,7 @@
     </row>
     <row r="1172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1172" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B1172">
         <v>4.7613599999999998</v>
@@ -13001,7 +12998,7 @@
     </row>
     <row r="1173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1173" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B1173">
         <v>4.8331099999999996</v>
@@ -13009,7 +13006,7 @@
     </row>
     <row r="1174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1174" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B1174">
         <v>4.82369</v>
@@ -13017,7 +13014,7 @@
     </row>
     <row r="1175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1175" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B1175">
         <v>4.8345700000000003</v>
@@ -13025,7 +13022,7 @@
     </row>
     <row r="1176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1176" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B1176">
         <v>4.8658999999999999</v>
@@ -13033,7 +13030,7 @@
     </row>
     <row r="1177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1177" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B1177">
         <v>4.9323300000000003</v>
@@ -13041,572 +13038,572 @@
     </row>
     <row r="1178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1178" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1179" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1180" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1181" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1182" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1183" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1184" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1185" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1185" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1186" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1186" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1187" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1187" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1188" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1188" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1189" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1189" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1190" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1190" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1191" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1191" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1192" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1192" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1193" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1193" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1194" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1194" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1195" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1195" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1196" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1196" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1197" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1197" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1198" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1198" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1199" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1199" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1200" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1200" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1201" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1201" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1202" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1202" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1203" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1203" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1204" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1204" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1205" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1205" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1206" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1206" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1207" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1207" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1208" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1208" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1209" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1209" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1210" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1210" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1211" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1211" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1212" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1212" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1213" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1213" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1214" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1214" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1215" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1215" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1216" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1216" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1217" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1217" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1218" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1218" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1219" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1219" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1220" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1220" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1221" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1221" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1222" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1222" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1223" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1223" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1224" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1224" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1225" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1225" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1226" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1226" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1227" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1227" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1228" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1228" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1229" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1229" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1230" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1230" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1231" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1231" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1232" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1232" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1233" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1233" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1234" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1234" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1235" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1235" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1236" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1236" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1237" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1237" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1238" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1238" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1239" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1239" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1240" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1240" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1241" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1241" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1242" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1242" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1243" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1243" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1244" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1244" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1245" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1245" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1246" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1246" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1247" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1247" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1248" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1248" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1249" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1249" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1250" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1250" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1251" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1251" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1252" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1252" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1253" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1253" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1254" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1254" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1255" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1255" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1256" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1256" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1257" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1257" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1258" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1258" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1259" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1259" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1260" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1260" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1261" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1261" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1262" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1262" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1263" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1263" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1264" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1264" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1265" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1265" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1266" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1266" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1267" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1267" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1268" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1268" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1269" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1269" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1270" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1270" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1271" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1271" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1272" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1272" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1273" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1273" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1274" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1274" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1275" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1275" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1276" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1276" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1277" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1277" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1278" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1278" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1279" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1279" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1280" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1280" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1281" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1281" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1282" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1282" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1283" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1283" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1284" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1284" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1285" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1285" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1286" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1286" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1287" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1287" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1288" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1288" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1289" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1289" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1290" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1290" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="1291" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1291" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
   </sheetData>
